--- a/Data/collapsed database manual cases/morelos_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/morelos_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8606EA-C578-8342-9B5D-09962A71FB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3E459D-93E1-314E-B218-582D3E9D09EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="571">
   <si>
     <t>uniqueid</t>
   </si>
@@ -1721,6 +1721,21 @@
   </si>
   <si>
     <t>https://www.jornada.com.mx/notas/2023/05/26/estados/se-suman-a-morena-presidentes-municipales-opositores-de-morelos/</t>
+  </si>
+  <si>
+    <t>EDUARDO CAMPOS ALLENDE</t>
+  </si>
+  <si>
+    <t>PAS</t>
+  </si>
+  <si>
+    <t>https://impepac.mx/wp-content/uploads/2018/Microsites/saber%20p%20votar/MUNICIPIO/MUNICIPIOS%20PDF/ZACUALPAN1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/p/1HMzw8CKoa/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100064950613003</t>
   </si>
 </sst>
 </file>
@@ -2088,7 +2103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S258"/>
+  <dimension ref="A1:S262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -13115,7 +13130,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>17007</v>
       </c>
@@ -13135,7 +13150,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>17014</v>
       </c>
@@ -13153,6 +13168,89 @@
       </c>
       <c r="I258" t="s">
         <v>565</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>17026</v>
+      </c>
+      <c r="B259">
+        <v>2024</v>
+      </c>
+      <c r="E259" t="s">
+        <v>567</v>
+      </c>
+      <c r="F259" t="s">
+        <v>566</v>
+      </c>
+      <c r="H259" t="s">
+        <v>567</v>
+      </c>
+      <c r="J259" t="s">
+        <v>567</v>
+      </c>
+      <c r="K259" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>17032</v>
+      </c>
+      <c r="B260">
+        <v>2021</v>
+      </c>
+      <c r="E260" t="s">
+        <v>526</v>
+      </c>
+      <c r="F260" t="s">
+        <v>527</v>
+      </c>
+      <c r="H260" t="s">
+        <v>32</v>
+      </c>
+      <c r="I260" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>17013</v>
+      </c>
+      <c r="B261">
+        <v>2021</v>
+      </c>
+      <c r="E261" t="s">
+        <v>528</v>
+      </c>
+      <c r="F261" t="s">
+        <v>223</v>
+      </c>
+      <c r="H261" t="s">
+        <v>111</v>
+      </c>
+      <c r="I261" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>17015</v>
+      </c>
+      <c r="B262">
+        <v>2021</v>
+      </c>
+      <c r="E262" t="s">
+        <v>528</v>
+      </c>
+      <c r="F262" t="s">
+        <v>529</v>
+      </c>
+      <c r="H262" t="s">
+        <v>530</v>
+      </c>
+      <c r="I262" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
